--- a/src/main/resources/Closeout_Field_Values.xlsx
+++ b/src/main/resources/Closeout_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22624"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MCPL#L92\Desktop\Automation projects\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Product\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{968FEB21-AC69-4D5E-9005-0D93B6E2FEBE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F1422EA-8E22-4242-A1BF-03D768B7A7E4}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11949" firstSheet="1" activeTab="3" xr2:uid="{53A78F2A-66A3-4C9D-BADA-DECB8EFCEB55}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{53A78F2A-66A3-4C9D-BADA-DECB8EFCEB55}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -25,17 +25,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="59">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -209,6 +204,9 @@
   </si>
   <si>
     <t>fieldJustification__c</t>
+  </si>
+  <si>
+    <t>fieldType__c</t>
   </si>
 </sst>
 </file>
@@ -580,14 +578,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D63121E-24A7-4605-825A-0B99C45876A1}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.69140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.07421875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -598,23 +596,23 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="C2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="C3" t="s">
         <v>7</v>
@@ -629,12 +627,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7BBCD17-F259-4C54-8AFE-639F1178A6AB}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="26.84375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -645,7 +643,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -656,7 +654,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -676,13 +674,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81A642DD-5C22-403F-AC5C-036497C62C6C}">
   <dimension ref="A1:C32"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="29.69140625" customWidth="1"/>
-    <col min="3" max="3" width="25.69140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.7109375" customWidth="1"/>
+    <col min="3" max="3" width="25.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -693,7 +691,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -704,7 +702,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -715,7 +713,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -726,7 +724,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -737,7 +735,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -748,7 +746,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -759,7 +757,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -770,7 +768,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -781,7 +779,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -792,7 +790,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -803,7 +801,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -814,7 +812,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -825,7 +823,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -836,7 +834,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>9</v>
       </c>
@@ -847,7 +845,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>9</v>
       </c>
@@ -858,7 +856,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>9</v>
       </c>
@@ -869,7 +867,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>9</v>
       </c>
@@ -880,7 +878,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>9</v>
       </c>
@@ -891,7 +889,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>9</v>
       </c>
@@ -902,7 +900,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>9</v>
       </c>
@@ -913,7 +911,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>9</v>
       </c>
@@ -924,7 +922,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>9</v>
       </c>
@@ -935,7 +933,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>9</v>
       </c>
@@ -946,7 +944,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>9</v>
       </c>
@@ -957,7 +955,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>9</v>
       </c>
@@ -968,7 +966,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>9</v>
       </c>
@@ -979,7 +977,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>9</v>
       </c>
@@ -990,7 +988,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>9</v>
       </c>
@@ -1001,7 +999,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>9</v>
       </c>
@@ -1012,7 +1010,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>9</v>
       </c>
@@ -1023,7 +1021,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -1043,13 +1041,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5F7DE33-22A9-4DFB-A132-6081F21423BE}">
   <dimension ref="A1:C32"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="30.69140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1060,7 +1058,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1071,7 +1069,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1082,7 +1080,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -1093,7 +1091,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -1104,7 +1102,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1115,7 +1113,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1126,7 +1124,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -1137,7 +1135,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -1148,7 +1146,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -1159,7 +1157,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1170,7 +1168,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>9</v>
       </c>
@@ -1181,7 +1179,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -1192,7 +1190,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -1203,7 +1201,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>9</v>
       </c>
@@ -1214,7 +1212,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>9</v>
       </c>
@@ -1225,7 +1223,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>9</v>
       </c>
@@ -1236,7 +1234,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>9</v>
       </c>
@@ -1247,7 +1245,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>9</v>
       </c>
@@ -1258,7 +1256,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>9</v>
       </c>
@@ -1269,7 +1267,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>9</v>
       </c>
@@ -1280,7 +1278,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>9</v>
       </c>
@@ -1291,7 +1289,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>9</v>
       </c>
@@ -1302,7 +1300,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>9</v>
       </c>
@@ -1313,7 +1311,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>9</v>
       </c>
@@ -1324,7 +1322,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>9</v>
       </c>
@@ -1335,7 +1333,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>9</v>
       </c>
@@ -1346,7 +1344,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>9</v>
       </c>
@@ -1357,7 +1355,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>9</v>
       </c>
@@ -1368,7 +1366,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>9</v>
       </c>
@@ -1379,7 +1377,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>9</v>
       </c>
@@ -1390,7 +1388,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -1410,13 +1408,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D229D022-2CD7-4F3C-BA00-D4F6DB9FA189}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="13.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1427,7 +1425,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>40</v>
       </c>
@@ -1446,14 +1444,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B11CE9E0-A984-444A-96CC-42B957DC3B9C}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.3046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.69140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.4609375" customWidth="1"/>
+    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1464,7 +1462,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>40</v>
       </c>

--- a/src/main/resources/Closeout_Field_Values.xlsx
+++ b/src/main/resources/Closeout_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25128"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C57FE6D2-BE44-4C65-B8F5-9A352BECF038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3813DCA2-B6E3-4473-B0F9-69CADD3E86FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{53A78F2A-66A3-4C9D-BADA-DECB8EFCEB55}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{53A78F2A-66A3-4C9D-BADA-DECB8EFCEB55}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -163,9 +163,6 @@
     <t>ChecklistQuestionPick6__c</t>
   </si>
   <si>
-    <t>fieldReason__c</t>
-  </si>
-  <si>
     <t>Checked</t>
   </si>
   <si>
@@ -205,7 +202,10 @@
     <t>fieldJustification__c</t>
   </si>
   <si>
-    <t>fieldType__c</t>
+    <t>Type__c</t>
+  </si>
+  <si>
+    <t>Reason__c</t>
   </si>
 </sst>
 </file>
@@ -583,15 +583,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D63121E-24A7-4605-825A-0B99C45876A1}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -602,27 +602,30 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
       </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B6" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -633,13 +636,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7BBCD17-F259-4C54-8AFE-639F1178A6AB}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -650,23 +653,23 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -681,13 +684,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81A642DD-5C22-403F-AC5C-036497C62C6C}">
   <dimension ref="A1:C32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="29.7109375" customWidth="1"/>
-    <col min="3" max="3" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.7265625" customWidth="1"/>
+    <col min="3" max="3" width="25.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -698,7 +701,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -709,7 +712,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -720,7 +723,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -731,7 +734,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -742,7 +745,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -753,7 +756,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -764,7 +767,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -775,7 +778,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -786,7 +789,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -797,7 +800,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -808,7 +811,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -819,7 +822,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -830,7 +833,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -841,7 +844,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -852,7 +855,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>7</v>
       </c>
@@ -863,7 +866,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>7</v>
       </c>
@@ -874,7 +877,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>7</v>
       </c>
@@ -885,7 +888,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -896,7 +899,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>7</v>
       </c>
@@ -907,7 +910,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>7</v>
       </c>
@@ -918,7 +921,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>7</v>
       </c>
@@ -929,7 +932,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>7</v>
       </c>
@@ -940,7 +943,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>7</v>
       </c>
@@ -951,7 +954,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>7</v>
       </c>
@@ -962,7 +965,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>7</v>
       </c>
@@ -973,7 +976,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>7</v>
       </c>
@@ -984,7 +987,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>7</v>
       </c>
@@ -995,7 +998,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>7</v>
       </c>
@@ -1006,7 +1009,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>7</v>
       </c>
@@ -1017,7 +1020,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>7</v>
       </c>
@@ -1028,12 +1031,12 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="C32" t="s">
         <v>14</v>
@@ -1048,13 +1051,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5F7DE33-22A9-4DFB-A132-6081F21423BE}">
   <dimension ref="A1:C32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1065,7 +1068,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -1076,7 +1079,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1087,7 +1090,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -1098,7 +1101,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1109,7 +1112,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1120,7 +1123,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -1131,18 +1134,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1153,7 +1156,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -1164,18 +1167,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>7</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -1186,7 +1189,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -1197,18 +1200,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>7</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C14" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -1219,7 +1222,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>7</v>
       </c>
@@ -1230,7 +1233,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>7</v>
       </c>
@@ -1241,7 +1244,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>7</v>
       </c>
@@ -1252,18 +1255,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>7</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C19" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>7</v>
       </c>
@@ -1274,7 +1277,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>7</v>
       </c>
@@ -1285,7 +1288,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>7</v>
       </c>
@@ -1296,7 +1299,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>7</v>
       </c>
@@ -1307,18 +1310,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>7</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C24" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>7</v>
       </c>
@@ -1329,7 +1332,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>7</v>
       </c>
@@ -1340,7 +1343,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>7</v>
       </c>
@@ -1351,18 +1354,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>7</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C28" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>7</v>
       </c>
@@ -1373,7 +1376,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>7</v>
       </c>
@@ -1384,26 +1387,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>7</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C31" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>38</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C32" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1415,13 +1418,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D229D022-2CD7-4F3C-BA00-D4F6DB9FA189}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1432,7 +1435,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -1451,14 +1454,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B11CE9E0-A984-444A-96CC-42B957DC3B9C}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.42578125" customWidth="1"/>
+    <col min="1" max="1" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1469,7 +1472,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -1477,7 +1480,7 @@
         <v>37</v>
       </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Closeout_Field_Values.xlsx
+++ b/src/main/resources/Closeout_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3813DCA2-B6E3-4473-B0F9-69CADD3E86FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0588B144-E225-46BC-8A4F-34E5CAD38DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{53A78F2A-66A3-4C9D-BADA-DECB8EFCEB55}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="5" xr2:uid="{53A78F2A-66A3-4C9D-BADA-DECB8EFCEB55}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="51">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -175,21 +175,6 @@
     <t>fieldComments2__c</t>
   </si>
   <si>
-    <t>fieldReportFinanceComments__c</t>
-  </si>
-  <si>
-    <t>fieldComments3__c</t>
-  </si>
-  <si>
-    <t>fieldComments5__c</t>
-  </si>
-  <si>
-    <t>fieldComments4__c</t>
-  </si>
-  <si>
-    <t>fieldComments6__c</t>
-  </si>
-  <si>
     <t>Automation Expense</t>
   </si>
   <si>
@@ -197,9 +182,6 @@
   </si>
   <si>
     <t>Automation Finance Comments</t>
-  </si>
-  <si>
-    <t>fieldJustification__c</t>
   </si>
   <si>
     <t>Type__c</t>
@@ -287,9 +269,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -327,7 +309,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -433,7 +415,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -575,7 +557,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -607,7 +589,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -618,7 +600,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -658,7 +640,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>43</v>
@@ -669,7 +651,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -1036,7 +1018,7 @@
         <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C32" t="s">
         <v>14</v>
@@ -1142,7 +1124,7 @@
         <v>44</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
@@ -1175,7 +1157,7 @@
         <v>45</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
@@ -1205,10 +1187,10 @@
         <v>7</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
@@ -1260,10 +1242,10 @@
         <v>7</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" t="s">
         <v>47</v>
-      </c>
-      <c r="C19" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
@@ -1315,10 +1297,10 @@
         <v>7</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="C24" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
@@ -1359,10 +1341,10 @@
         <v>7</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="C28" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
@@ -1392,10 +1374,10 @@
         <v>7</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="C31" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
@@ -1403,10 +1385,10 @@
         <v>38</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="C32" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Closeout_Field_Values.xlsx
+++ b/src/main/resources/Closeout_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0588B144-E225-46BC-8A4F-34E5CAD38DE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F90A8BAF-DDCC-4A5B-9F2D-20271DE0FA22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="5" xr2:uid="{53A78F2A-66A3-4C9D-BADA-DECB8EFCEB55}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{53A78F2A-66A3-4C9D-BADA-DECB8EFCEB55}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -28,6 +28,12 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -566,14 +572,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D63121E-24A7-4605-825A-0B99C45876A1}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -584,7 +590,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -595,7 +601,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -606,7 +612,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B6" s="4"/>
     </row>
   </sheetData>
@@ -618,13 +624,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7BBCD17-F259-4C54-8AFE-639F1178A6AB}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="15.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -635,7 +641,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -646,7 +652,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -666,13 +672,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81A642DD-5C22-403F-AC5C-036497C62C6C}">
   <dimension ref="A1:C32"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="29.7265625" customWidth="1"/>
-    <col min="3" max="3" width="25.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.77734375" customWidth="1"/>
+    <col min="3" max="3" width="25.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -683,7 +689,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -694,7 +700,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -705,7 +711,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -716,7 +722,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -727,7 +733,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -738,7 +744,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -749,7 +755,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -760,7 +766,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -771,7 +777,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -782,7 +788,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -793,7 +799,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -804,7 +810,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -815,7 +821,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -826,7 +832,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -837,7 +843,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>7</v>
       </c>
@@ -848,7 +854,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>7</v>
       </c>
@@ -859,7 +865,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>7</v>
       </c>
@@ -870,7 +876,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -881,7 +887,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>7</v>
       </c>
@@ -892,7 +898,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>7</v>
       </c>
@@ -903,7 +909,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>7</v>
       </c>
@@ -914,7 +920,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>7</v>
       </c>
@@ -925,7 +931,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>7</v>
       </c>
@@ -936,7 +942,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>7</v>
       </c>
@@ -947,7 +953,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>7</v>
       </c>
@@ -958,7 +964,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>7</v>
       </c>
@@ -969,7 +975,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>7</v>
       </c>
@@ -980,7 +986,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>7</v>
       </c>
@@ -991,7 +997,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>7</v>
       </c>
@@ -1002,7 +1008,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>7</v>
       </c>
@@ -1013,7 +1019,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>38</v>
       </c>
@@ -1033,13 +1039,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5F7DE33-22A9-4DFB-A132-6081F21423BE}">
   <dimension ref="A1:C32"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="30.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1050,7 +1056,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -1061,7 +1067,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -1072,7 +1078,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -1083,7 +1089,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1094,7 +1100,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1105,7 +1111,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -1116,7 +1122,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -1127,7 +1133,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1138,7 +1144,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -1149,7 +1155,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -1160,7 +1166,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>7</v>
       </c>
@@ -1171,7 +1177,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>7</v>
       </c>
@@ -1182,7 +1188,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>7</v>
       </c>
@@ -1193,7 +1199,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>7</v>
       </c>
@@ -1204,7 +1210,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>7</v>
       </c>
@@ -1215,7 +1221,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>7</v>
       </c>
@@ -1226,7 +1232,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>7</v>
       </c>
@@ -1237,7 +1243,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>7</v>
       </c>
@@ -1248,7 +1254,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>7</v>
       </c>
@@ -1259,7 +1265,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>7</v>
       </c>
@@ -1270,7 +1276,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>7</v>
       </c>
@@ -1281,7 +1287,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>7</v>
       </c>
@@ -1292,7 +1298,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>7</v>
       </c>
@@ -1303,7 +1309,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>7</v>
       </c>
@@ -1314,7 +1320,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>7</v>
       </c>
@@ -1325,7 +1331,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>7</v>
       </c>
@@ -1336,7 +1342,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>7</v>
       </c>
@@ -1347,7 +1353,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>7</v>
       </c>
@@ -1358,7 +1364,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>7</v>
       </c>
@@ -1369,7 +1375,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>7</v>
       </c>
@@ -1380,7 +1386,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>38</v>
       </c>
@@ -1400,13 +1406,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D229D022-2CD7-4F3C-BA00-D4F6DB9FA189}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1417,7 +1423,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -1436,14 +1442,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B11CE9E0-A984-444A-96CC-42B957DC3B9C}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.453125" customWidth="1"/>
+    <col min="1" max="1" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1454,7 +1460,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>38</v>
       </c>

--- a/src/main/resources/Closeout_Field_Values.xlsx
+++ b/src/main/resources/Closeout_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F90A8BAF-DDCC-4A5B-9F2D-20271DE0FA22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1C8844B-2E5F-4200-8BE5-F218DAD11346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{53A78F2A-66A3-4C9D-BADA-DECB8EFCEB55}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="49">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -173,12 +173,6 @@
   </si>
   <si>
     <t>Termination</t>
-  </si>
-  <si>
-    <t>fieldExpensesComments__c</t>
-  </si>
-  <si>
-    <t>fieldComments2__c</t>
   </si>
   <si>
     <t>Automation Expense</t>
@@ -595,7 +589,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C2" t="s">
         <v>4</v>
@@ -606,7 +600,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -646,7 +640,7 @@
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>43</v>
@@ -657,7 +651,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -1024,7 +1018,7 @@
         <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C32" t="s">
         <v>14</v>
@@ -1127,10 +1121,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
         <v>44</v>
-      </c>
-      <c r="C8" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -1160,10 +1154,10 @@
         <v>7</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" t="s">
         <v>45</v>
-      </c>
-      <c r="C11" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -1196,7 +1190,7 @@
         <v>20</v>
       </c>
       <c r="C14" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
@@ -1251,7 +1245,7 @@
         <v>25</v>
       </c>
       <c r="C19" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -1306,7 +1300,7 @@
         <v>39</v>
       </c>
       <c r="C24" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
@@ -1350,7 +1344,7 @@
         <v>33</v>
       </c>
       <c r="C28" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.3">
@@ -1383,7 +1377,7 @@
         <v>36</v>
       </c>
       <c r="C31" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.3">
@@ -1394,7 +1388,7 @@
         <v>40</v>
       </c>
       <c r="C32" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Closeout_Field_Values.xlsx
+++ b/src/main/resources/Closeout_Field_Values.xlsx
@@ -1,24 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1C8844B-2E5F-4200-8BE5-F218DAD11346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9EC3618-F4A4-495D-AC1F-95B9CA16C3F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{53A78F2A-66A3-4C9D-BADA-DECB8EFCEB55}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="4" xr2:uid="{53A78F2A-66A3-4C9D-BADA-DECB8EFCEB55}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
-    <sheet name="TerminationValues" sheetId="5" r:id="rId2"/>
-    <sheet name="Edition" sheetId="2" r:id="rId3"/>
-    <sheet name="TerminationEdition" sheetId="6" r:id="rId4"/>
-    <sheet name="Override" sheetId="4" r:id="rId5"/>
-    <sheet name="Subrecipient fields" sheetId="3" r:id="rId6"/>
+    <sheet name="Grantee_Creation" sheetId="7" r:id="rId2"/>
+    <sheet name="TerminationValues" sheetId="5" r:id="rId3"/>
+    <sheet name="Edition" sheetId="2" r:id="rId4"/>
+    <sheet name="Grantee_Edition" sheetId="8" r:id="rId5"/>
+    <sheet name="TerminationEdition" sheetId="6" r:id="rId6"/>
+    <sheet name="Override" sheetId="4" r:id="rId7"/>
+    <sheet name="Subrecipient fields" sheetId="3" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="72">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -188,13 +190,82 @@
   </si>
   <si>
     <t>Reason__c</t>
+  </si>
+  <si>
+    <t>CloseoutDate__c</t>
+  </si>
+  <si>
+    <t>PleaseExplainUnspentBalance__c</t>
+  </si>
+  <si>
+    <t>ReviewExpenditures__c</t>
+  </si>
+  <si>
+    <t>IdentifyAllOutstandingInvoices__c</t>
+  </si>
+  <si>
+    <t>PayrollExpenses__c</t>
+  </si>
+  <si>
+    <t>Ensurejournalentriescompleted__c</t>
+  </si>
+  <si>
+    <t>IdentifyOutstandinginvoices__c</t>
+  </si>
+  <si>
+    <t>ConfirmIndirectExpensesHaveBeenPost__c</t>
+  </si>
+  <si>
+    <t>ReviewAndUpdatePersonnelAllocations__c</t>
+  </si>
+  <si>
+    <t>RemoveGATsFromVariousSundrySystems__c</t>
+  </si>
+  <si>
+    <t>ReviewedPurchaseOrdersIfClosed__c</t>
+  </si>
+  <si>
+    <t>EnsureCostSharingcommitmentsmet__c</t>
+  </si>
+  <si>
+    <t>AllFinancialReportingRequirements__c</t>
+  </si>
+  <si>
+    <t>EnsureCostSharingCommitmentsAreMet__c</t>
+  </si>
+  <si>
+    <t>AllProgressReportingRequirements__c</t>
+  </si>
+  <si>
+    <t>FinalFFRforAllFunds__c</t>
+  </si>
+  <si>
+    <t>IsThereAnUnspentBalance__c</t>
+  </si>
+  <si>
+    <t>AdvancePayments__c</t>
+  </si>
+  <si>
+    <t>HaveTheRealPropertyStatus__c</t>
+  </si>
+  <si>
+    <t>HastheTangiblePersonalProperty__c</t>
+  </si>
+  <si>
+    <t>ConfirmAllAuditConcernsMonitoring__c</t>
+  </si>
+  <si>
+    <t>HaveAllFederalMonitoringFindings__c</t>
+  </si>
+  <si>
+    <t>HaveAllApplicableFederalGrant__c</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -220,6 +291,12 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -241,7 +318,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -251,6 +328,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -616,6 +694,64 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAC8419F-7EF0-4E2C-ACDF-F7C16D39F622}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="14.88671875" customWidth="1"/>
+    <col min="3" max="3" width="28.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7BBCD17-F259-4C54-8AFE-639F1178A6AB}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -663,7 +799,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81A642DD-5C22-403F-AC5C-036497C62C6C}">
   <dimension ref="A1:C32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1030,7 +1166,285 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B57E1A21-52CD-4C4C-8D79-62BBACF8FE4A}">
+  <dimension ref="A1:C24"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="36.5546875" customWidth="1"/>
+    <col min="3" max="3" width="36.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C21" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>7</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C23" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5F7DE33-22A9-4DFB-A132-6081F21423BE}">
   <dimension ref="A1:C32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1397,7 +1811,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D229D022-2CD7-4F3C-BA00-D4F6DB9FA189}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1433,7 +1847,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B11CE9E0-A984-444A-96CC-42B957DC3B9C}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/src/main/resources/Closeout_Field_Values.xlsx
+++ b/src/main/resources/Closeout_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9EC3618-F4A4-495D-AC1F-95B9CA16C3F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23477C24-C249-4A0F-947F-025A49B70D1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="4" xr2:uid="{53A78F2A-66A3-4C9D-BADA-DECB8EFCEB55}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="73">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -259,6 +259,9 @@
   </si>
   <si>
     <t>HaveAllApplicableFederalGrant__c</t>
+  </si>
+  <si>
+    <t>Check List</t>
   </si>
 </sst>
 </file>
@@ -748,6 +751,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1171,6 +1175,7 @@
   <dimension ref="A1:C24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="18.6640625" customWidth="1"/>
     <col min="2" max="2" width="36.5546875" customWidth="1"/>
     <col min="3" max="3" width="36.33203125" customWidth="1"/>
   </cols>
@@ -1188,7 +1193,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>51</v>
@@ -1199,7 +1204,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>52</v>
@@ -1210,7 +1215,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>53</v>
@@ -1221,7 +1226,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>54</v>
@@ -1232,7 +1237,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>55</v>
@@ -1243,7 +1248,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>56</v>
@@ -1254,7 +1259,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="B8" t="s">
         <v>57</v>
@@ -1265,7 +1270,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>58</v>
@@ -1276,7 +1281,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>59</v>
@@ -1287,7 +1292,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>60</v>
@@ -1298,7 +1303,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>61</v>
@@ -1309,7 +1314,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>62</v>
@@ -1320,7 +1325,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>50</v>
@@ -1331,7 +1336,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>63</v>
@@ -1342,7 +1347,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>64</v>
@@ -1353,7 +1358,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>65</v>
@@ -1364,7 +1369,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>66</v>
@@ -1375,7 +1380,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>67</v>
@@ -1386,7 +1391,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>68</v>
@@ -1397,7 +1402,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>69</v>
@@ -1408,7 +1413,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>70</v>
@@ -1419,7 +1424,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>71</v>

--- a/src/main/resources/Closeout_Field_Values.xlsx
+++ b/src/main/resources/Closeout_Field_Values.xlsx
@@ -1,24 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1C8844B-2E5F-4200-8BE5-F218DAD11346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23477C24-C249-4A0F-947F-025A49B70D1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{53A78F2A-66A3-4C9D-BADA-DECB8EFCEB55}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="4" xr2:uid="{53A78F2A-66A3-4C9D-BADA-DECB8EFCEB55}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
-    <sheet name="TerminationValues" sheetId="5" r:id="rId2"/>
-    <sheet name="Edition" sheetId="2" r:id="rId3"/>
-    <sheet name="TerminationEdition" sheetId="6" r:id="rId4"/>
-    <sheet name="Override" sheetId="4" r:id="rId5"/>
-    <sheet name="Subrecipient fields" sheetId="3" r:id="rId6"/>
+    <sheet name="Grantee_Creation" sheetId="7" r:id="rId2"/>
+    <sheet name="TerminationValues" sheetId="5" r:id="rId3"/>
+    <sheet name="Edition" sheetId="2" r:id="rId4"/>
+    <sheet name="Grantee_Edition" sheetId="8" r:id="rId5"/>
+    <sheet name="TerminationEdition" sheetId="6" r:id="rId6"/>
+    <sheet name="Override" sheetId="4" r:id="rId7"/>
+    <sheet name="Subrecipient fields" sheetId="3" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="73">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -188,13 +190,85 @@
   </si>
   <si>
     <t>Reason__c</t>
+  </si>
+  <si>
+    <t>CloseoutDate__c</t>
+  </si>
+  <si>
+    <t>PleaseExplainUnspentBalance__c</t>
+  </si>
+  <si>
+    <t>ReviewExpenditures__c</t>
+  </si>
+  <si>
+    <t>IdentifyAllOutstandingInvoices__c</t>
+  </si>
+  <si>
+    <t>PayrollExpenses__c</t>
+  </si>
+  <si>
+    <t>Ensurejournalentriescompleted__c</t>
+  </si>
+  <si>
+    <t>IdentifyOutstandinginvoices__c</t>
+  </si>
+  <si>
+    <t>ConfirmIndirectExpensesHaveBeenPost__c</t>
+  </si>
+  <si>
+    <t>ReviewAndUpdatePersonnelAllocations__c</t>
+  </si>
+  <si>
+    <t>RemoveGATsFromVariousSundrySystems__c</t>
+  </si>
+  <si>
+    <t>ReviewedPurchaseOrdersIfClosed__c</t>
+  </si>
+  <si>
+    <t>EnsureCostSharingcommitmentsmet__c</t>
+  </si>
+  <si>
+    <t>AllFinancialReportingRequirements__c</t>
+  </si>
+  <si>
+    <t>EnsureCostSharingCommitmentsAreMet__c</t>
+  </si>
+  <si>
+    <t>AllProgressReportingRequirements__c</t>
+  </si>
+  <si>
+    <t>FinalFFRforAllFunds__c</t>
+  </si>
+  <si>
+    <t>IsThereAnUnspentBalance__c</t>
+  </si>
+  <si>
+    <t>AdvancePayments__c</t>
+  </si>
+  <si>
+    <t>HaveTheRealPropertyStatus__c</t>
+  </si>
+  <si>
+    <t>HastheTangiblePersonalProperty__c</t>
+  </si>
+  <si>
+    <t>ConfirmAllAuditConcernsMonitoring__c</t>
+  </si>
+  <si>
+    <t>HaveAllFederalMonitoringFindings__c</t>
+  </si>
+  <si>
+    <t>HaveAllApplicableFederalGrant__c</t>
+  </si>
+  <si>
+    <t>Check List</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -220,6 +294,12 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -241,7 +321,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -251,6 +331,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -616,6 +697,65 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAC8419F-7EF0-4E2C-ACDF-F7C16D39F622}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="14.88671875" customWidth="1"/>
+    <col min="3" max="3" width="28.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7BBCD17-F259-4C54-8AFE-639F1178A6AB}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -663,7 +803,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81A642DD-5C22-403F-AC5C-036497C62C6C}">
   <dimension ref="A1:C32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1030,7 +1170,286 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B57E1A21-52CD-4C4C-8D79-62BBACF8FE4A}">
+  <dimension ref="A1:C24"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="18.6640625" customWidth="1"/>
+    <col min="2" max="2" width="36.5546875" customWidth="1"/>
+    <col min="3" max="3" width="36.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>72</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>72</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>72</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>72</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>72</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>72</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="C16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>72</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C17" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>72</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>72</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>72</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C21" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>72</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="C22" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>72</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C23" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5F7DE33-22A9-4DFB-A132-6081F21423BE}">
   <dimension ref="A1:C32"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1397,7 +1816,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D229D022-2CD7-4F3C-BA00-D4F6DB9FA189}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1433,7 +1852,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B11CE9E0-A984-444A-96CC-42B957DC3B9C}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/src/main/resources/Closeout_Field_Values.xlsx
+++ b/src/main/resources/Closeout_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Cleanup_Projects\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23477C24-C249-4A0F-947F-025A49B70D1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5997615C-A0F4-489B-9086-BB74822E3E2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="4" xr2:uid="{53A78F2A-66A3-4C9D-BADA-DECB8EFCEB55}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="1" activeTab="4" xr2:uid="{53A78F2A-66A3-4C9D-BADA-DECB8EFCEB55}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="71">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -244,12 +244,6 @@
   </si>
   <si>
     <t>AdvancePayments__c</t>
-  </si>
-  <si>
-    <t>HaveTheRealPropertyStatus__c</t>
-  </si>
-  <si>
-    <t>HastheTangiblePersonalProperty__c</t>
   </si>
   <si>
     <t>ConfirmAllAuditConcernsMonitoring__c</t>
@@ -1172,7 +1166,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B57E1A21-52CD-4C4C-8D79-62BBACF8FE4A}">
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18.6640625" customWidth="1"/>
@@ -1193,7 +1187,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>51</v>
@@ -1204,7 +1198,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>52</v>
@@ -1215,7 +1209,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>53</v>
@@ -1226,7 +1220,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>54</v>
@@ -1237,7 +1231,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>55</v>
@@ -1248,7 +1242,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>56</v>
@@ -1259,7 +1253,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B8" t="s">
         <v>57</v>
@@ -1270,7 +1264,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>58</v>
@@ -1281,7 +1275,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>59</v>
@@ -1292,7 +1286,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>60</v>
@@ -1303,7 +1297,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>61</v>
@@ -1314,7 +1308,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>62</v>
@@ -1325,7 +1319,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>50</v>
@@ -1336,7 +1330,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>63</v>
@@ -1347,7 +1341,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>64</v>
@@ -1358,7 +1352,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>65</v>
@@ -1369,7 +1363,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>66</v>
@@ -1380,7 +1374,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>67</v>
@@ -1391,7 +1385,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>68</v>
@@ -1402,7 +1396,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>69</v>
@@ -1413,34 +1407,12 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>72</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>70</v>
+        <v>38</v>
+      </c>
+      <c r="B22" t="s">
+        <v>40</v>
       </c>
       <c r="C22" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>72</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C23" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" t="s">
         <v>14</v>
       </c>
     </row>
